--- a/data/official_data/knowledge/programme_master.xlsx
+++ b/data/official_data/knowledge/programme_master.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="418">
   <si>
     <t>Programme</t>
   </si>
@@ -258,21 +258,12 @@
     <t>Computer Applications (BCA/MCA)</t>
   </si>
   <si>
-    <t>Integrated B.Sc. B.Ed.</t>
-  </si>
-  <si>
     <t>Institute of Advanced Studies in Education</t>
   </si>
   <si>
     <t>4 Years (8 Semesters)</t>
   </si>
   <si>
-    <t>Integrated B.A. B.Ed.</t>
-  </si>
-  <si>
-    <t>Integrated B.Ed.-M.Ed.</t>
-  </si>
-  <si>
     <t>3 Years (6 Semesters)</t>
   </si>
   <si>
@@ -325,9 +316,6 @@
   </si>
   <si>
     <t>Postgraduate</t>
-  </si>
-  <si>
-    <t>MEd</t>
   </si>
   <si>
     <t>School of Sciences</t>
@@ -1236,9 +1224,6 @@
     <t>Integrated BCA-MCA</t>
   </si>
   <si>
-    <t>Integrated MA (Journalism &amp; Mass Communication)</t>
-  </si>
-  <si>
     <t>40 Merit+12 SF</t>
   </si>
   <si>
@@ -1429,9 +1414,6 @@
     <t>Master of Education is a two-year postgraduate programme that develops advanced knowledge of educational psychology, curriculum studies, educational technology, assessment and evaluation, research methodology, educational administration, and teacher education. It prepares graduates for careers in teacher education, educational leadership, curriculum development, research, and doctoral studies.</t>
   </si>
   <si>
-    <t>M.Ed.</t>
-  </si>
-  <si>
     <t>Bachelor's Degree from any UGC-recognized University with at least 50% marks (45% for Reserved Categories).</t>
   </si>
   <si>
@@ -1538,6 +1520,186 @@
   </si>
   <si>
     <t xml:space="preserve">abdul ahad azad memorial college </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated MA </t>
+  </si>
+  <si>
+    <t>subject_overview</t>
+  </si>
+  <si>
+    <t>English at Cluster University Srinagar is a humanities subject that combines language skills with the study of literature. It develops students' listening, speaking, reading and writing abilities while introducing them to poetry, prose, drama, literary devices, genres, critical analysis, academic writing and communication. The programme aims to improve students' language proficiency, creativity, analytical thinking, presentation skills and appreciation of literature.</t>
+  </si>
+  <si>
+    <t>Economics at Cluster University Srinagar is the study of how scarce resources are allocated and how individuals, markets and governments make economic decisions. The subject covers microeconomics, macroeconomics, national income, money and banking, inflation, unemployment, economic development, poverty, inequality, public policy and mathematical economic analysis. It develops students' ability to understand economic problems, analyse data and evaluate economic policies.</t>
+  </si>
+  <si>
+    <t>Political Science at Cluster University Srinagar is the study of politics, government, political institutions, political theories and relationships between states. The subject covers areas such as political theory, the Indian Constitution, Indian government and politics, comparative politics, international relations, public administration, democracy, governance and human rights. It helps students develop critical thinking, analytical skills and a deeper understanding of political systems and contemporary political issues.</t>
+  </si>
+  <si>
+    <t>History at Cluster University Srinagar focuses on the study of past events, societies, civilizations, cultures, political developments and social transformations. Students learn about ancient, medieval and modern history, with particular emphasis on the history of India and the Kashmir region. The subject develops students' ability to analyse historical sources, understand cause-and-effect relationships and interpret political, social, economic and cultural changes over time.</t>
+  </si>
+  <si>
+    <t>Sociology at Cluster University Srinagar is the systematic study of society, social relationships, institutions, groups and social change. Students examine how individuals interact with society and how factors such as family, education, religion, economy and politics influence social life. The subject also explores social problems, inequality, culture and contemporary social issues.</t>
+  </si>
+  <si>
+    <t>Education at Cluster University Srinagar focuses on the study of teaching, learning, educational systems and the development of individuals and society. Students learn about educational theories, philosophies, psychology of learning, curriculum, teaching methods, assessment and educational administration. The subject prepares students to understand and analyse educational processes and challenges.</t>
+  </si>
+  <si>
+    <t>Psychology at Cluster University Srinagar focuses on the scientific study of human behaviour and mental processes. Students learn how people think, learn, perceive, remember and interact with others. The subject covers major psychological theories and applications and helps students develop an understanding of human personality, emotions, motivation and behaviour.</t>
+  </si>
+  <si>
+    <t>Computer Applications focuses on the practical use of computers and software to solve problems and manage information. It covers programming, databases, web technologies, computer networks, software development and information systems. The subject develops programming, problem-solving and technical skills.</t>
+  </si>
+  <si>
+    <t>Physics is the study of matter, energy, motion and their interactions. It covers mechanics, thermodynamics, waves, optics, electricity, magnetism, electronics and modern physics. The subject develops analytical, mathematical and experimental skills for understanding physical phenomena.</t>
+  </si>
+  <si>
+    <t>Chemistry is the study of matter, its composition, properties, structure and chemical reactions. It covers organic, inorganic and physical chemistry along with laboratory techniques and chemical analysis. The subject develops experimental and analytical skills for understanding chemical processes.</t>
+  </si>
+  <si>
+    <t>Mathematics focuses on the study of numbers, structures, patterns, quantities and logical relationships. It covers areas such as algebra, calculus, geometry, differential equations, statistics and mathematical analysis. The subject develops logical reasoning, problem-solving and quantitative skills.</t>
+  </si>
+  <si>
+    <t>Botany is the scientific study of plants, including their structure, classification, growth, reproduction and functions. It covers plant physiology, taxonomy, ecology, genetics, evolution and plant diversity. The subject develops knowledge of plant biology through theoretical and practical study.</t>
+  </si>
+  <si>
+    <t>Zoology is the scientific study of animals, their structure, physiology, behaviour, evolution and classification. It covers animal diversity, genetics, ecology, evolution, physiology and developmental biology. The subject develops an understanding of animal life through theoretical and laboratory-based study.</t>
+  </si>
+  <si>
+    <t>Biotechnology combines biology with technology to develop products and processes using living organisms, cells and biological molecules. It covers molecular biology, genetics, microbiology, genetic engineering, cell culture and biotechnology applications. The subject provides knowledge and practical skills for applications in medicine, agriculture, industry and research.</t>
+  </si>
+  <si>
+    <t>Environmental Science is the interdisciplinary study of the environment and the interactions between living organisms and their surroundings. It covers ecosystems, biodiversity, natural resources, pollution, climate change, environmental management and conservation. The subject develops awareness and skills for addressing environmental challenges.</t>
+  </si>
+  <si>
+    <t>Information Technology (IT) focuses on the use of computers, software, networks and digital technologies to store, process, manage and communicate information. It covers programming, databases, networking, web technologies, cybersecurity and information systems. The subject develops technical and problem-solving skills for applying IT in various fields.</t>
+  </si>
+  <si>
+    <t>Biochemistry is the study of the chemical processes and molecules that occur in living organisms. It covers biomolecules, enzymes, metabolism, molecular biology, genetics and biochemical techniques. The subject helps students understand the chemical basis of life and its applications in medicine, biotechnology and research.</t>
+  </si>
+  <si>
+    <t>Journalism and Mass Communication focuses on gathering, producing and communicating information through print, television, radio, digital media and other platforms. It covers reporting, writing, editing, broadcasting, media production, public relations and media ethics. The subject develops communication, research and media-production skills.</t>
+  </si>
+  <si>
+    <t>Arabic focuses on the study of the Arabic language, literature and culture. It covers grammar, vocabulary, reading, writing, translation, classical and modern Arabic literature. The subject develops language proficiency and an understanding of Arabic literary and cultural traditions.</t>
+  </si>
+  <si>
+    <t>Urdu focuses on the study of the Urdu language, literature and literary traditions. It covers grammar, poetry, prose, fiction, criticism, linguistics and translation. The subject develops language proficiency, literary appreciation and critical understanding of Urdu literature.</t>
+  </si>
+  <si>
+    <t>Kashmiri focuses on the study of the Kashmiri language, literature, culture and literary heritage. It covers language structure, poetry, prose, folklore, literary criticism and the development of Kashmiri literature. The subject promotes linguistic knowledge and appreciation of Kashmir's cultural heritage.</t>
+  </si>
+  <si>
+    <t>Philosophy is the systematic study of fundamental questions concerning knowledge, reality, existence, morality and human reasoning. It covers logic, ethics, metaphysics, epistemology, social and political philosophy and major philosophical traditions. The subject develops critical thinking, logical reasoning and analytical skills.</t>
+  </si>
+  <si>
+    <t>Public Administration focuses on the study and management of government organizations, public policies and administrative processes. It covers administrative theory, governance, public policy, Indian administration, financial administration and local government. The subject develops an understanding of how public institutions function and deliver services to society.</t>
+  </si>
+  <si>
+    <t>Islamic Studies focuses on the study of Islam, its beliefs, teachings, history and intellectual traditions. It covers the Quran, Hadith, Islamic jurisprudence, Islamic history, ethics and Islamic culture. The subject develops an understanding of Islamic thought, values and historical development.</t>
+  </si>
+  <si>
+    <t>Music focuses on the study and practice of musical traditions, theory and performance. It covers musical notation, rhythm, melody, composition, vocal and instrumental techniques, music history and appreciation. The subject develops musical knowledge, creativity and performance skills.</t>
+  </si>
+  <si>
+    <t>Social Work focuses on helping individuals, families and communities address social challenges and improve their well-being. It covers social welfare, community development, counselling, social casework, group work, social policy and fieldwork. The subject develops communication, problem-solving and community-service skills.</t>
+  </si>
+  <si>
+    <t>Geography is the study of the Earth's physical features, human societies and their interactions with the environment. It covers physical geography, human geography, climatology, geomorphology, population, resources, regional geography and geographic techniques. The subject develops spatial analysis and understanding of environmental and human processes.</t>
+  </si>
+  <si>
+    <t>Statistics focuses on collecting, organizing, analysing and interpreting data to support decision-making. It covers probability, statistical distributions, sampling, estimation, hypothesis testing, regression, correlation and statistical methods. The subject develops quantitative, analytical and data-interpretation skills.</t>
+  </si>
+  <si>
+    <t>Geology is the scientific study of the Earth, its materials, structure, history and geological processes. It covers minerals, rocks, fossils, plate tectonics, geomorphology, structural geology and Earth's evolution. The subject develops practical and analytical skills for understanding geological resources and natural processes.</t>
+  </si>
+  <si>
+    <t>Electronics focuses on the study, design and application of electronic circuits and systems. It covers semiconductor devices, analog and digital circuits, communication systems, microprocessors, instrumentation and electronic devices. The subject develops practical and technical skills in electronic system design and analysis.</t>
+  </si>
+  <si>
+    <t>Water Management focuses on the sustainable use, conservation and management of water resources. It covers hydrology, water quality, water conservation, irrigation, groundwater, watershed management and water-resource planning. The subject develops knowledge and skills for addressing water scarcity and sustainable resource management.</t>
+  </si>
+  <si>
+    <t>Clinical Biochemistry applies biochemical principles to the diagnosis and monitoring of diseases. It covers analysis of blood, urine and other biological samples, enzymes, hormones, glucose, lipids, proteins and clinical biomarkers. The subject develops laboratory and analytical skills used in healthcare and diagnostic services.</t>
+  </si>
+  <si>
+    <t>Food Science and Technology focuses on the scientific principles involved in the production, processing, preservation, safety and quality of food. It covers food chemistry, microbiology, nutrition, food processing, packaging and quality control. The subject develops knowledge and practical skills for the food industry and food safety.</t>
+  </si>
+  <si>
+    <t>Home Science is an interdisciplinary subject concerned with nutrition, health, family resources, human development and well-being. It covers food and nutrition, human development, textiles and clothing, resource management and community development. The subject develops practical and scientific skills for improving individual, family and community well-being.</t>
+  </si>
+  <si>
+    <t>Political Science at Cluster University Srinagar focuses on the systematic study of government, politics, political institutions, political ideas, constitutions, public administration, and international relations. It helps students understand how political systems function, how governments make decisions, and how citizens participate in democratic processes.</t>
+  </si>
+  <si>
+    <r>
+      <t>Information Technology (IT)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> focuses on the use of computers, software, networks and digital technologies to store, process, manage and communicate information. It covers programming, databases, networking, web technologies, cybersecurity and information systems. The subject develops technical and problem-solving skills for applying IT in various fields.</t>
+    </r>
+  </si>
+  <si>
+    <t>Artificial Intelligence and Machine Learning (AI &amp; ML) focuses on developing systems that can perform tasks requiring human-like intelligence, such as learning, reasoning, prediction and decision-making. It covers machine learning, neural networks, natural language processing, computer vision and intelligent systems. The subject develops programming, data analysis and problem-solving skills for building AI-based applications.</t>
+  </si>
+  <si>
+    <t>Data Science focuses on collecting, processing, analysing and interpreting data to discover useful patterns and support decision-making. It covers statistics, programming, data visualization, databases, machine learning and data analysis. The subject develops skills for extracting meaningful insights from structured and unstructured data.</t>
+  </si>
+  <si>
+    <r>
+      <t>Political Science at Cluster University Srinagar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> focuses on the systematic study of government, politics, political institutions, political ideas, constitutions, public administration, and international relations. It helps students understand how political systems function, how governments make decisions, and how citizens participate in democratic processes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Commerce focuses on the study of business, trade, finance and economic activities. It covers accounting, business economics, management, taxation, financial management, marketing and business law. The subject develops financial, analytical and business-management skills for careers in commerce and related fields.</t>
+  </si>
+  <si>
+    <t>Business Administration focuses on the principles and practices involved in managing organizations and businesses. It covers management, marketing, finance, human resources, operations, entrepreneurship and business strategy. The subject develops leadership, decision-making, communication and managerial skills for effective business administration.</t>
+  </si>
+  <si>
+    <t>Education focuses on the study of teaching, learning and the development of individuals and society. It covers educational psychology, teaching methods, curriculum development, assessment and evaluation, educational technology, guidance and counselling, inclusive education and educational administration. The subject develops knowledge and skills for effective teaching, learning and educational practice.</t>
+  </si>
+  <si>
+    <t>M.Ed</t>
+  </si>
+  <si>
+    <t>To pursue a Bachelor of Education (B.Ed) at Cluster University of Srinagar, candidates must hold a graduation or post-graduation degree in Science, Social Sciences, Humanities, or Commerce from a recognized university with a minimum of 50% marks (45% for reserved categories)</t>
+  </si>
+  <si>
+    <t>Selection is based on entrance tests like CUET or JKBOPEE</t>
+  </si>
+  <si>
+    <t>B.Ed. (Bachelor of Education) at Cluster University Srinagar is a teacher-education programme designed to develop professional knowledge, teaching skills and competencies required for effective classroom practice. The programme covers educational psychology, philosophical and sociological foundations of education, curriculum and pedagogy, teaching-learning methods, assessment and evaluation, educational technology, guidance and counselling, inclusive education and school-based practical experiences. It prepares students to understand learners, plan and deliver effective instruction, assess learning outcomes and address diverse educational needs.</t>
+  </si>
+  <si>
+    <t>Integrated BEd MEd</t>
+  </si>
+  <si>
+    <t>Integrated BA BEd</t>
+  </si>
+  <si>
+    <t>Integrated BSc BEd</t>
+  </si>
+  <si>
+    <t>BEd</t>
   </si>
 </sst>
 </file>
@@ -1685,7 +1847,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1796,6 +1958,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2099,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:S139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="5" customWidth="1"/>
@@ -2115,12 +2280,13 @@
     <col min="12" max="12" width="7" customWidth="1"/>
     <col min="13" max="13" width="18.42578125" customWidth="1"/>
     <col min="14" max="14" width="27.7109375" customWidth="1"/>
-    <col min="15" max="15" width="30.42578125" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="17" max="17" width="16.42578125" customWidth="1"/>
+    <col min="15" max="16" width="30.42578125" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="16.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2140,43 +2306,46 @@
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="S1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="233.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
@@ -2196,43 +2365,46 @@
         <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1">
         <v>40</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="R2" s="2">
+      <c r="R2" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="2">
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="270" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -2252,37 +2424,43 @@
         <v>18</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K3" s="5">
         <v>80</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="P3" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="300" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
@@ -2302,37 +2480,43 @@
         <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K4" s="5">
         <v>120</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="300" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
@@ -2352,37 +2536,43 @@
         <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K5" s="18">
         <v>80</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="300" x14ac:dyDescent="0.25">
+      <c r="R5" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
@@ -2402,37 +2592,43 @@
         <v>18</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K6" s="5">
         <v>60</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="P6" s="19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="225" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>6</v>
       </c>
@@ -2452,37 +2648,43 @@
         <v>18</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K7" s="5">
         <v>80</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="225" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="P7" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -2502,16 +2704,16 @@
         <v>18</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K8" s="20">
         <v>120</v>
@@ -2520,19 +2722,25 @@
         <v>10358</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="R8" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
@@ -2552,37 +2760,43 @@
         <v>18</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="P9" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>6</v>
       </c>
@@ -2602,37 +2816,43 @@
         <v>18</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K10">
         <v>270</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>19</v>
       </c>
@@ -2652,42 +2872,48 @@
         <v>23</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K11">
         <v>220</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="P11" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>15</v>
@@ -2702,37 +2928,43 @@
         <v>24</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K12">
         <v>40</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="P12" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="225" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
@@ -2752,34 +2984,40 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K13">
         <v>80</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>29</v>
       </c>
@@ -2799,37 +3037,43 @@
         <v>23</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K14">
         <v>60</v>
       </c>
       <c r="L14" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q14" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="P14" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="R14" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>29</v>
       </c>
@@ -2849,37 +3093,43 @@
         <v>24</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K15">
         <v>60</v>
       </c>
       <c r="L15" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q15" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="P15" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="R15" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>29</v>
       </c>
@@ -2899,37 +3149,43 @@
         <v>32</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K16">
         <v>60</v>
       </c>
       <c r="L16" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q16" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="P16" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="210" x14ac:dyDescent="0.25">
+      <c r="R16" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>33</v>
       </c>
@@ -2949,37 +3205,43 @@
         <v>36</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I17" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="P17" s="17" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="P17" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q17" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>33</v>
       </c>
@@ -2999,37 +3261,43 @@
         <v>36</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="P18" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="180" x14ac:dyDescent="0.25">
+      <c r="P18" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>33</v>
       </c>
@@ -3049,37 +3317,43 @@
         <v>38</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I19" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="P19" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="180" x14ac:dyDescent="0.25">
+      <c r="P19" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>33</v>
       </c>
@@ -3096,40 +3370,46 @@
         <v>37</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="195" x14ac:dyDescent="0.25">
+      <c r="P20" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q20" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>33</v>
       </c>
@@ -3146,40 +3426,46 @@
         <v>37</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="P21" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="225" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q21" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>33</v>
       </c>
@@ -3196,40 +3482,46 @@
         <v>39</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I22" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K22" s="20">
         <v>60</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P22" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="225" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="129" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>33</v>
       </c>
@@ -3246,40 +3538,46 @@
         <v>39</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K23" s="20">
         <v>60</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P23" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="225" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q23" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>33</v>
       </c>
@@ -3296,40 +3594,46 @@
         <v>39</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="P24" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="225" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q24" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>33</v>
       </c>
@@ -3346,40 +3650,46 @@
         <v>40</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I25" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K25" s="20">
         <v>100</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="P25" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="225" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q25" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="138.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>33</v>
       </c>
@@ -3396,40 +3706,46 @@
         <v>40</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K26" s="20">
         <v>70</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="P26" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="225" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q26" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>33</v>
       </c>
@@ -3446,40 +3762,46 @@
         <v>40</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K27" s="20">
         <v>160</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="P27" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="210.75" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q27" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="131.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>33</v>
       </c>
@@ -3496,40 +3818,46 @@
         <v>41</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G28" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I28" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K28" s="20">
         <v>140</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="210.75" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="Q28" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="133.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>33</v>
       </c>
@@ -3546,40 +3874,46 @@
         <v>41</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K29" s="20">
         <v>70</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O29" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="P29" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="211.5" thickBot="1" x14ac:dyDescent="0.35">
+        <v>380</v>
+      </c>
+      <c r="Q29" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>33</v>
       </c>
@@ -3596,40 +3930,46 @@
         <v>41</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K30" s="20">
         <v>160</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="Q30" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>33</v>
       </c>
@@ -3649,37 +3989,43 @@
         <v>44</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I31" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K31" s="22">
         <v>70</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="P31" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q31" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="77.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>33</v>
       </c>
@@ -3690,7 +4036,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>42</v>
@@ -3699,37 +4045,43 @@
         <v>32</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K32" s="22">
         <v>70</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="P32" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q32" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>33</v>
       </c>
@@ -3740,7 +4092,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>43</v>
@@ -3749,37 +4101,43 @@
         <v>32</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K33" s="23">
         <v>100</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P33" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q33" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>33</v>
       </c>
@@ -3799,37 +4157,43 @@
         <v>32</v>
       </c>
       <c r="G34" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H34" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I34" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K34" s="23">
         <v>60</v>
       </c>
       <c r="L34" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P34" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q34" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>33</v>
       </c>
@@ -3849,37 +4213,43 @@
         <v>32</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K35" s="23">
         <v>50</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P35" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q35" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="111" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>33</v>
       </c>
@@ -3890,7 +4260,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>43</v>
@@ -3899,37 +4269,43 @@
         <v>32</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K36" s="23">
         <v>120</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P36" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" ht="380.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q36" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" s="2" customFormat="1" ht="380.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>33</v>
       </c>
@@ -3949,37 +4325,43 @@
         <v>47</v>
       </c>
       <c r="G37" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="H37" s="31" t="s">
-        <v>104</v>
-      </c>
       <c r="I37" s="32" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K37" s="28">
         <v>90</v>
       </c>
       <c r="L37" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="M37" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="N37" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q37" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="M37" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="N37" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>33</v>
       </c>
@@ -3999,37 +4381,43 @@
         <v>47</v>
       </c>
       <c r="G38" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H38" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I38" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K38" s="23">
         <v>50</v>
       </c>
       <c r="L38" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M38" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="204.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>33</v>
       </c>
@@ -4049,37 +4437,43 @@
         <v>47</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K39" s="23">
         <v>80</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M39" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="N39" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="N39" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P39" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>6</v>
       </c>
@@ -4099,37 +4493,43 @@
         <v>54</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K40" s="23">
         <v>80</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M40" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="126.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q40" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>6</v>
       </c>
@@ -4149,37 +4549,43 @@
         <v>47</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K41" s="23">
         <v>80</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M41" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="135.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q41" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="135.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>6</v>
       </c>
@@ -4199,37 +4605,43 @@
         <v>47</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K42" s="23">
         <v>80</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M42" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q42" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>6</v>
       </c>
@@ -4249,37 +4661,43 @@
         <v>47</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K43" s="23">
         <v>80</v>
       </c>
       <c r="L43" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M43" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N43" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>6</v>
       </c>
@@ -4299,37 +4717,43 @@
         <v>47</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K44" t="s">
+        <v>189</v>
+      </c>
+      <c r="L44" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="M44" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="N44" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="O44" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="K44" t="s">
-        <v>193</v>
-      </c>
-      <c r="L44" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="M44" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="N44" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P44" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>6</v>
       </c>
@@ -4349,37 +4773,43 @@
         <v>47</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K45" s="23">
         <v>60</v>
       </c>
       <c r="L45" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M45" s="27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="123" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>6</v>
       </c>
@@ -4399,37 +4829,43 @@
         <v>47</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K46" s="23">
         <v>80</v>
       </c>
       <c r="L46" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>6</v>
       </c>
@@ -4449,37 +4885,43 @@
         <v>47</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K47" s="23">
         <v>110</v>
       </c>
       <c r="L47" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>6</v>
       </c>
@@ -4499,37 +4941,43 @@
         <v>47</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K48" s="23">
         <v>80</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>6</v>
       </c>
@@ -4549,37 +4997,43 @@
         <v>47</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K49" s="23">
         <v>80</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q49" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>6</v>
       </c>
@@ -4599,37 +5053,43 @@
         <v>47</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K50" s="20">
         <v>60</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>6</v>
       </c>
@@ -4649,37 +5109,43 @@
         <v>47</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K51" s="20">
         <v>80</v>
       </c>
       <c r="L51" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>6</v>
       </c>
@@ -4699,37 +5165,43 @@
         <v>47</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K52" s="20">
         <v>80</v>
       </c>
       <c r="L52" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P52" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>6</v>
       </c>
@@ -4749,37 +5221,43 @@
         <v>47</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K53" s="20">
         <v>80</v>
       </c>
       <c r="L53" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O53" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="O53" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P53" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="120.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>6</v>
       </c>
@@ -4799,37 +5277,43 @@
         <v>47</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K54" s="20">
         <v>120</v>
       </c>
       <c r="L54" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>6</v>
       </c>
@@ -4849,37 +5333,43 @@
         <v>47</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K55" s="20">
         <v>120</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q55" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>6</v>
       </c>
@@ -4899,37 +5389,43 @@
         <v>47</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K56" s="20">
         <v>30</v>
       </c>
       <c r="L56" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>6</v>
       </c>
@@ -4949,37 +5445,43 @@
         <v>47</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K57" s="20">
         <v>80</v>
       </c>
       <c r="L57" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>6</v>
       </c>
@@ -4999,37 +5501,43 @@
         <v>47</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K58" t="s">
+        <v>189</v>
+      </c>
+      <c r="L58" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L58" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O58" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q58" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>6</v>
       </c>
@@ -5049,37 +5557,43 @@
         <v>47</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K59" t="s">
+        <v>189</v>
+      </c>
+      <c r="L59" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N59" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L59" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O59" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q59" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>6</v>
       </c>
@@ -5099,37 +5613,43 @@
         <v>47</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s">
+        <v>189</v>
+      </c>
+      <c r="L60" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L60" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O60" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>6</v>
       </c>
@@ -5149,37 +5669,43 @@
         <v>47</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J61" s="35" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K61" s="20">
         <v>120</v>
       </c>
       <c r="L61" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="P61" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q61" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>6</v>
       </c>
@@ -5199,37 +5725,43 @@
         <v>47</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J62" s="35" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K62">
         <v>180</v>
       </c>
       <c r="L62" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>6</v>
       </c>
@@ -5249,37 +5781,43 @@
         <v>47</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J63" s="35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K63">
         <v>50</v>
       </c>
       <c r="L63" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="P63" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q63" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>6</v>
       </c>
@@ -5299,37 +5837,43 @@
         <v>47</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J64" s="35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K64">
         <v>50</v>
       </c>
       <c r="L64" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q64" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>6</v>
       </c>
@@ -5349,37 +5893,43 @@
         <v>47</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J65" s="35" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K65">
         <v>60</v>
       </c>
       <c r="L65" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q65" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>6</v>
       </c>
@@ -5399,37 +5949,43 @@
         <v>47</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J66" s="35" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K66">
         <v>80</v>
       </c>
       <c r="L66" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q66" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>6</v>
       </c>
@@ -5449,37 +6005,43 @@
         <v>47</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K67">
         <v>80</v>
       </c>
       <c r="L67" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q67" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>6</v>
       </c>
@@ -5499,37 +6061,43 @@
         <v>47</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K68">
         <v>120</v>
       </c>
       <c r="L68" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="P68" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q68" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>6</v>
       </c>
@@ -5549,37 +6117,43 @@
         <v>47</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K69">
         <v>30</v>
       </c>
       <c r="L69" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="P69" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q69" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>6</v>
       </c>
@@ -5599,42 +6173,48 @@
         <v>47</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K70">
         <v>30</v>
       </c>
       <c r="L70" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="P70" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q70" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>15</v>
@@ -5649,42 +6229,48 @@
         <v>47</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H71" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I71" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K71">
         <v>30</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>15</v>
@@ -5699,37 +6285,43 @@
         <v>47</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K72">
         <v>30</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q72" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>33</v>
       </c>
@@ -5749,37 +6341,43 @@
         <v>47</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K73">
         <v>40</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="P73" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q73" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>33</v>
       </c>
@@ -5799,37 +6397,43 @@
         <v>47</v>
       </c>
       <c r="G74" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H74" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H74" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I74" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K74">
         <v>60</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="P74" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q74" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>33</v>
       </c>
@@ -5849,37 +6453,43 @@
         <v>47</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H75" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H75" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I75" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J75" s="35" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K75">
         <v>30</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="P75" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q75" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>33</v>
       </c>
@@ -5899,37 +6509,43 @@
         <v>47</v>
       </c>
       <c r="G76" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H76" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I76" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J76" s="36" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K76">
         <v>30</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q76" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>33</v>
       </c>
@@ -5949,37 +6565,43 @@
         <v>47</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="K77" t="s">
+        <v>189</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N77" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L77" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O77" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q77" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>33</v>
       </c>
@@ -5999,37 +6621,43 @@
         <v>47</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K78" t="s">
+        <v>189</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="N78" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L78" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O78" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="167.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q78" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="167.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>33</v>
       </c>
@@ -6049,37 +6677,43 @@
         <v>47</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J79" s="35" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K79">
         <v>200</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="P79" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q79" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>33</v>
       </c>
@@ -6099,37 +6733,43 @@
         <v>47</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K80">
         <v>70</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q80" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>33</v>
       </c>
@@ -6149,37 +6789,43 @@
         <v>47</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H81" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="I81" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K81">
         <v>60</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="P81" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q81" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>33</v>
       </c>
@@ -6199,37 +6845,43 @@
         <v>47</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K82">
         <v>70</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="P82" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q82" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>71</v>
       </c>
@@ -6252,34 +6904,40 @@
         <v>72</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="P83" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q83" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>71</v>
       </c>
@@ -6302,34 +6960,40 @@
         <v>72</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K84" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="P84" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="153" customHeight="1" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q84" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>71</v>
       </c>
@@ -6352,34 +7016,40 @@
         <v>72</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K85" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="O85" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="L85" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="P85" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P85" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q85" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>71</v>
       </c>
@@ -6402,34 +7072,40 @@
         <v>72</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K86" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L86" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="O86" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="M86" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="P86" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P86" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q86" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>71</v>
       </c>
@@ -6452,34 +7128,40 @@
         <v>72</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="P87" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="P87" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q87" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>71</v>
       </c>
@@ -6502,34 +7184,40 @@
         <v>72</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="P88" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q88" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>71</v>
       </c>
@@ -6552,34 +7240,40 @@
         <v>72</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="P89" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q89" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>71</v>
       </c>
@@ -6602,34 +7296,40 @@
         <v>72</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K90" s="17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="P90" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="P90" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q90" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>75</v>
       </c>
@@ -6652,34 +7352,40 @@
         <v>72</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="P91" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q91" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>75</v>
       </c>
@@ -6702,34 +7408,40 @@
         <v>72</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J92" s="34" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="P92" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="P92" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q92" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>75</v>
       </c>
@@ -6752,34 +7464,40 @@
         <v>72</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="K93" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="P93" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="P93" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q93" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>75</v>
       </c>
@@ -6802,34 +7520,40 @@
         <v>72</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="P94" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q94" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>75</v>
       </c>
@@ -6852,34 +7576,40 @@
         <v>72</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="K95" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="P95" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="P95" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q95" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="147" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>76</v>
       </c>
@@ -6902,39 +7632,45 @@
         <v>72</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="K96" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="P96" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q96" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>72</v>
@@ -6952,36 +7688,42 @@
         <v>72</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="P97" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="177" customHeight="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="P97" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q97" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>79</v>
@@ -7002,36 +7744,42 @@
         <v>72</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="P98" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="163.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="P98" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q98" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>51</v>
@@ -7052,36 +7800,42 @@
         <v>72</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J99" s="36" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="P99" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="203.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="P99" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q99" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>26</v>
@@ -7090,48 +7844,54 @@
         <v>72</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J100" s="35" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="K100" s="37">
         <v>50</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="P100" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q100" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>26</v>
@@ -7140,48 +7900,54 @@
         <v>72</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J101" s="35" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K101" s="37">
         <v>50</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="P101" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q101" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>26</v>
@@ -7190,54 +7956,60 @@
         <v>72</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>72</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J102" s="35" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="P102" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q102" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>35</v>
@@ -7246,148 +8018,166 @@
         <v>46</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H103" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="M103" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N103" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O103" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="P103" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q103" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D104" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I103" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J103" s="3" t="s">
+      <c r="E104" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="M104" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N104" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O104" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="K103" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="M103" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N103" s="3" t="s">
+      <c r="P104" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q104" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J105" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="O103" s="3" t="s">
+      <c r="K105" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L105" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="M105" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O105" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="P103" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I104" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="K104" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="M104" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="P104" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="174" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I105" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L105" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="M105" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O105" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="P105" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P105" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q105" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D106" s="12" t="s">
         <v>35</v>
@@ -7396,48 +8186,54 @@
         <v>37</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L106" s="17" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M106" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="P106" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="P106" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q106" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D107" s="12" t="s">
         <v>35</v>
@@ -7446,48 +8242,54 @@
         <v>34</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M107" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="P107" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="P107" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q107" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D108" s="12" t="s">
         <v>35</v>
@@ -7496,48 +8298,54 @@
         <v>40</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M108" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="P108" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="P108" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q108" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D109" s="12" t="s">
         <v>35</v>
@@ -7546,48 +8354,54 @@
         <v>41</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M109" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="P109" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="P109" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q109" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>74</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>35</v>
@@ -7596,48 +8410,54 @@
         <v>74</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M110" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="P110" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="P110" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q110" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>35</v>
@@ -7646,48 +8466,54 @@
         <v>43</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M111" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="P111" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="P111" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q111" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R111" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>16</v>
@@ -7696,48 +8522,54 @@
         <v>70</v>
       </c>
       <c r="F112" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M112" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N112" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="P112" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q112" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M112" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O112" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="P112" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>16</v>
@@ -7746,48 +8578,54 @@
         <v>7</v>
       </c>
       <c r="F113" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="M113" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="P113" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q113" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R113" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L113" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="M113" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O113" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="P113" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>16</v>
@@ -7796,48 +8634,54 @@
         <v>9</v>
       </c>
       <c r="F114" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="M114" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N114" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="P114" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q114" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L114" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="M114" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N114" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O114" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="P114" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>17</v>
@@ -7846,48 +8690,54 @@
         <v>11</v>
       </c>
       <c r="F115" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M115" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="P115" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q115" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L115" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M115" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N115" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O115" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="P115" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>17</v>
@@ -7896,48 +8746,54 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M116" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="P116" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q116" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M116" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O116" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="P116" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>17</v>
@@ -7946,48 +8802,54 @@
         <v>51</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G117" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H117" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H117" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I117" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M117" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="P117" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="P117" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q117" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B118" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>17</v>
@@ -7996,48 +8858,52 @@
         <v>20</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G118" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H118" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H118" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I118" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M118" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="P118" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R118" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>17</v>
@@ -8046,48 +8912,52 @@
         <v>27</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G119" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H119" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H119" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I119" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="P119" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="P119" s="3"/>
+      <c r="Q119" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>30</v>
@@ -8096,98 +8966,110 @@
         <v>31</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M120" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="P120" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="P120" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q120" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R120" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
       <c r="B121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E121" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M121" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="P121" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q121" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>35</v>
@@ -8196,48 +9078,54 @@
         <v>46</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M122" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="P122" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="P122" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q122" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R122" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D123" s="12" t="s">
         <v>35</v>
@@ -8246,48 +9134,54 @@
         <v>37</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M123" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="P123" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q123" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R123" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D124" s="12" t="s">
         <v>35</v>
@@ -8296,48 +9190,54 @@
         <v>34</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M124" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="P124" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="P124" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q124" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R124" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B125" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>35</v>
@@ -8346,48 +9246,54 @@
         <v>40</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M125" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="P125" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="P125" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q125" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R125" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>35</v>
@@ -8396,48 +9302,54 @@
         <v>41</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M126" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="P126" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="P126" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q126" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R126" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>74</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D127" s="12" t="s">
         <v>35</v>
@@ -8446,48 +9358,54 @@
         <v>74</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M127" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="P127" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="P127" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q127" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R127" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D128" s="12" t="s">
         <v>35</v>
@@ -8496,148 +9414,166 @@
         <v>43</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H128" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M128" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="P128" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q128" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R128" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D129" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I128" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="K128" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L128" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M128" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N128" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O128" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="P128" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C129" s="10" t="s">
+      <c r="E129" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L129" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M129" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="N129" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="O129" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="P129" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q129" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R129" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B130" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D129" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F129" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H129" s="5" t="s">
+      <c r="C130" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D130" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I129" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="K129" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="L129" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M129" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N129" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="O129" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="P129" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="150.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="E130" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M130" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="P130" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="P130" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q130" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R130" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>16</v>
@@ -8646,48 +9582,54 @@
         <v>7</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M131" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="P131" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="P131" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q131" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R131" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D132" s="12" t="s">
         <v>16</v>
@@ -8696,48 +9638,54 @@
         <v>9</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="P132" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="P132" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q132" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R132" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B133" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>17</v>
@@ -8746,48 +9694,54 @@
         <v>10</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G133" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H133" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H133" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I133" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M133" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="P133" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="P133" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q133" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R133" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B134" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>17</v>
@@ -8796,48 +9750,54 @@
         <v>11</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G134" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H134" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H134" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I134" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M134" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="P134" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="P134" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q134" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R134" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>17</v>
@@ -8846,48 +9806,54 @@
         <v>20</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G135" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H135" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H135" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I135" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="P135" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="P135" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q135" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R135" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B136" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>17</v>
@@ -8896,48 +9862,54 @@
         <v>27</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G136" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H136" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H136" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="I136" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M136" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="P136" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="P136" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q136" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R136" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D137" s="12" t="s">
         <v>30</v>
@@ -8946,97 +9918,167 @@
         <v>31</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="P137" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="P137" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q137" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R137" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>103</v>
+        <v>410</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="M138" s="17" t="s">
-        <v>290</v>
+        <v>312</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="P138" s="17" t="s">
-        <v>131</v>
+        <v>362</v>
+      </c>
+      <c r="P138" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q138" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R138" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I139" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M139" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N139" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="P139" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q139" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="R139" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1"/>
+    <hyperlink ref="R2" r:id="rId1"/>
     <hyperlink ref="J76" r:id="rId2" display="https://www.careers360.com/colleges/sri-pratap-college-srinagar/bsc-water-management-course"/>
     <hyperlink ref="J99" r:id="rId3" display="https://www.cusrinagar.edu.in/"/>
+    <hyperlink ref="R3:R138" r:id="rId4" display="https://www.cusrinagar.edu.in"/>
+    <hyperlink ref="R139" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
